--- a/docs/fundacheck_reference.xlsx
+++ b/docs/fundacheck_reference.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Sales | Revenue | Total Revenue | Net Sales | Net Revenue | Sales Revenue | Revenue from Operations | Revenue from Operations (Net) | Revenue from Operations / Sales | Operating Revenue | Operating Revenues | Turnover | Net Turnover | Total Sales | Gross Sales | Sales Revenue from Operations | Income from Operations</t>
+          <t>Sales | Revenue from Operations | Revenue from Operations (Net) | Revenue from Operations / Sales | Sales Revenue from Operations | Net Sales | Operating Revenue | Operating Revenues | Turnover | Net Turnover | Total Sales | Gross Sales | Income from Operations | Sales Revenue | Revenue | Total Revenue | Net Revenue</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -749,11 +749,11 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Depreciation | Depreciation Expense | Depreciation &amp; Amortisation | Depreciation and Amortization | Depreciation &amp; Amortization | Depreciation / Amortisation | D&amp;A</t>
+          <t>Depreciation | Depreciation Expense | Depreciation &amp; Amortisation | Depreciation and Amortization | Depreciation &amp; Amortization | Depreciation / Amortisation | D&amp;A | Depreciation and Amortization Expense | Depreciation and Amortisation Expense | Depreciation &amp; Amortisation Expense | Depreciation, Amortisation and Impairment Expense | Depreciation and Depletion</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -924,11 +924,11 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Reserves | Reserves &amp; Surplus | Reserves and Surplus | Other Reserves | Other Equity</t>
+          <t>Reserves | Reserves &amp; Surplus | Reserves and Surplus | Other Reserves | Other Equity | Total Reserves and Surplus</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -1324,11 +1324,11 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Cash from Investing Activity | Cash from Investing Activities | Investing Cash Flow | Net Cash from Investing Activities | Cash Flow from Investing Activities</t>
+          <t>Cash from Investing Activity | Cash from Investing Activities | Investing Cash Flow | Net Cash from Investing Activities | Cash Flow from Investing Activities | Net Cash Used in Investing Activities | Net Cash Used In / From Investing Activities</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -1349,11 +1349,11 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Cash from Financing Activity | Cash from Financing Activities | Financing Cash Flow | Net Cash from Financing Activities | Cash Flow from Financing Activities</t>
+          <t>Cash from Financing Activity | Cash from Financing Activities | Financing Cash Flow | Net Cash from Financing Activities | Cash Flow from Financing Activities | Net Cash Used in Financing Activities | Net Cash Used In / From Financing Activities</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Flow | Net Increase in Cash | Net Increase / (Decrease) in Cash | Net Change in Cash</t>
+          <t>Net Cash Flow | Net Increase in Cash | Net Increase / (Decrease) in Cash | Net Change in Cash | Net Increase / (Decrease) in Cash and Cash Equivalents | Net (Decrease) / Increase in Cash and Cash Equivalents | Net Increase in Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Dividend Amount ÷ Net Profit</t>
+          <t>|Dividend Amount| ÷ Net Profit</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
